--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I511"/>
+  <dimension ref="A1:I516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17297,6 +17297,171 @@
         <v>349.09</v>
       </c>
       <c r="I511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="C512" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="D512" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="E512" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="F512" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="G512" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="H512" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="C513" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="D513" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="E513" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="F513" t="n">
+        <v>363.69</v>
+      </c>
+      <c r="G513" t="n">
+        <v>355.92</v>
+      </c>
+      <c r="H513" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>371.14</v>
+      </c>
+      <c r="C514" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="D514" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="E514" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="F514" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="G514" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="H514" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="C515" t="n">
+        <v>376.22</v>
+      </c>
+      <c r="D515" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="E515" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="F515" t="n">
+        <v>364.21</v>
+      </c>
+      <c r="G515" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="H515" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C516" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="D516" t="n">
+        <v>374.86</v>
+      </c>
+      <c r="E516" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="F516" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="G516" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="H516" t="n">
+        <v>349</v>
+      </c>
+      <c r="I516" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17313,7 +17478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22656,6 +22821,46 @@
       </c>
       <c r="B534" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -22824,28 +23029,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07488821767706945</v>
+        <v>-0.07899716157891874</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005072383844320849</v>
+        <v>0.005738124989236315</v>
       </c>
       <c r="M2" t="n">
-        <v>6.837513878170018</v>
+        <v>6.79187620707918</v>
       </c>
       <c r="N2" t="n">
-        <v>71.41423280723625</v>
+        <v>70.7851849126144</v>
       </c>
       <c r="O2" t="n">
-        <v>8.450694220431611</v>
+        <v>8.413393186617062</v>
       </c>
       <c r="P2" t="n">
-        <v>375.4498490576596</v>
+        <v>375.4908242003543</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22902,28 +23107,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1057595795501151</v>
+        <v>0.1074169267100565</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00772446556784967</v>
+        <v>0.008109727765536645</v>
       </c>
       <c r="M3" t="n">
-        <v>7.306524339285309</v>
+        <v>7.247390669240287</v>
       </c>
       <c r="N3" t="n">
-        <v>93.278527954914</v>
+        <v>92.38286247217715</v>
       </c>
       <c r="O3" t="n">
-        <v>9.658080966471237</v>
+        <v>9.611600411595207</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3395722343436</v>
+        <v>372.3230360838004</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22980,28 +23185,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07064645291786303</v>
+        <v>0.06884433136067705</v>
       </c>
       <c r="J4" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004517327670211069</v>
+        <v>0.004367187511217785</v>
       </c>
       <c r="M4" t="n">
-        <v>6.534715085450364</v>
+        <v>6.479538744516999</v>
       </c>
       <c r="N4" t="n">
-        <v>71.40214265782841</v>
+        <v>70.73304396113875</v>
       </c>
       <c r="O4" t="n">
-        <v>8.44997885546635</v>
+        <v>8.410293928343929</v>
       </c>
       <c r="P4" t="n">
-        <v>373.003116351528</v>
+        <v>373.0210643686372</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23058,28 +23263,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07712655615005909</v>
+        <v>0.08146466048197666</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004507691328741958</v>
+        <v>0.005112791533568029</v>
       </c>
       <c r="M5" t="n">
-        <v>7.017135659773383</v>
+        <v>6.98229171674887</v>
       </c>
       <c r="N5" t="n">
-        <v>85.37694703672385</v>
+        <v>84.624664522895</v>
       </c>
       <c r="O5" t="n">
-        <v>9.239964666421828</v>
+        <v>9.199166512401817</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6487696294427</v>
+        <v>366.6054753307266</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23136,28 +23341,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05504464427673501</v>
+        <v>0.06256558052619172</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002153987289316373</v>
+        <v>0.002824929724881131</v>
       </c>
       <c r="M6" t="n">
-        <v>7.895315435067672</v>
+        <v>7.870670987949344</v>
       </c>
       <c r="N6" t="n">
-        <v>91.21337059570966</v>
+        <v>90.53913538528164</v>
       </c>
       <c r="O6" t="n">
-        <v>9.550569124178395</v>
+        <v>9.515205483082415</v>
       </c>
       <c r="P6" t="n">
-        <v>357.4129975108249</v>
+        <v>357.3379524863809</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23214,28 +23419,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00613928564954999</v>
+        <v>0.01613652328200399</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>3.175898563989588e-05</v>
+        <v>0.0002222958957578403</v>
       </c>
       <c r="M7" t="n">
-        <v>6.917420764424016</v>
+        <v>6.91417859108035</v>
       </c>
       <c r="N7" t="n">
-        <v>77.11932880556506</v>
+        <v>76.73501148186028</v>
       </c>
       <c r="O7" t="n">
-        <v>8.781761144870945</v>
+        <v>8.759852252284869</v>
       </c>
       <c r="P7" t="n">
-        <v>349.2548077388122</v>
+        <v>349.1550677243249</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23292,28 +23497,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05112970512427594</v>
+        <v>-0.04235048530085078</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00303538731799835</v>
+        <v>0.002111618812369875</v>
       </c>
       <c r="M8" t="n">
-        <v>5.869268582421035</v>
+        <v>5.864188311453071</v>
       </c>
       <c r="N8" t="n">
-        <v>55.74303552613092</v>
+        <v>55.48452088201581</v>
       </c>
       <c r="O8" t="n">
-        <v>7.466125871302394</v>
+        <v>7.448793250051703</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9387734014493</v>
+        <v>345.851195057041</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23351,7 +23556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I511"/>
+  <dimension ref="A1:I516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47359,6 +47564,241 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-41.07741574439266,172.10314836417913</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-41.07675045364225,172.10296261912458</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-41.0760742472579,172.102898748519</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-41.07539963172014,172.10281702763976</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-41.074719348684766,172.10279854639563</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-41.074039397391736,172.10277628068772</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-41.07336226431542,172.1027224527834</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-41.07741679189689,172.10313666130304</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-41.07675058061082,172.10296120060823</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-41.07607525242379,172.1028875187128</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-41.07540145159271,172.10279669598705</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-41.07472160237017,172.10277336850484</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-41.0740414394689,172.10275346715417</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-41.07336415826178,172.1027012943347</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-41.077417183388064,172.10313228750076</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-41.07675067583723,172.10296013672098</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-41.07607677604155,172.10287049669014</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-41.07540252023712,172.10278475705098</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-41.074722141984175,172.10276733999555</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-41.07404169340565,172.102750630238</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-41.073363872582966,172.10270448583265</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-41.07741746907069,172.1031290958072</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-41.0767506440951,172.10296049135005</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-41.07607718868759,172.1028658865589</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-41.07540262604344,172.10278357497808</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-41.07472215256484,172.10276722178946</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-41.074041714567045,172.1027503938283</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-41.07336355516197,172.10270803194143</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-41.07741745848985,172.10312921401805</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-41.07675078164436,172.10295895462403</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-41.076077283913584,172.10286482268245</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-41.07540222397938,172.10278806685506</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-41.07472191979021,172.1027698223229</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-41.07404117495139,172.10275642227515</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-41.07336216908896,172.102723516616</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I516"/>
+  <dimension ref="A1:I520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17464,6 +17464,138 @@
       <c r="I516" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="C517" t="n">
+        <v>377.02</v>
+      </c>
+      <c r="D517" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="E517" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="F517" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="G517" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="H517" t="n">
+        <v>348.28</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="C518" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="D518" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="E518" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="F518" t="n">
+        <v>364</v>
+      </c>
+      <c r="G518" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="H518" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>373.29</v>
+      </c>
+      <c r="C519" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="D519" t="n">
+        <v>375.55</v>
+      </c>
+      <c r="E519" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="F519" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="G519" t="n">
+        <v>356</v>
+      </c>
+      <c r="H519" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="C520" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="D520" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="E520" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="F520" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="G520" t="n">
+        <v>357</v>
+      </c>
+      <c r="H520" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22861,6 +22993,46 @@
       </c>
       <c r="B538" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -23029,28 +23201,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07899716157891874</v>
+        <v>-0.07934661948627919</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005738124989236315</v>
+        <v>0.005870661014617085</v>
       </c>
       <c r="M2" t="n">
-        <v>6.79187620707918</v>
+        <v>6.741940356135151</v>
       </c>
       <c r="N2" t="n">
-        <v>70.7851849126144</v>
+        <v>70.24117562476445</v>
       </c>
       <c r="O2" t="n">
-        <v>8.413393186617062</v>
+        <v>8.381000872495148</v>
       </c>
       <c r="P2" t="n">
-        <v>375.4908242003543</v>
+        <v>375.4943188849992</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23107,28 +23279,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1074169267100565</v>
+        <v>0.1098740149396563</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008109727765536645</v>
+        <v>0.008599109083750722</v>
       </c>
       <c r="M3" t="n">
-        <v>7.247390669240287</v>
+        <v>7.208809990927251</v>
       </c>
       <c r="N3" t="n">
-        <v>92.38286247217715</v>
+        <v>91.69905562041549</v>
       </c>
       <c r="O3" t="n">
-        <v>9.611600411595207</v>
+        <v>9.57596238612159</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3230360838004</v>
+        <v>372.2984249820402</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23185,28 +23357,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06884433136067705</v>
+        <v>0.06974309697128321</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004367187511217785</v>
+        <v>0.004544753503518351</v>
       </c>
       <c r="M4" t="n">
-        <v>6.479538744516999</v>
+        <v>6.436165600640996</v>
       </c>
       <c r="N4" t="n">
-        <v>70.73304396113875</v>
+        <v>70.19285242181309</v>
       </c>
       <c r="O4" t="n">
-        <v>8.410293928343929</v>
+        <v>8.378117474815753</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0210643686372</v>
+        <v>373.0120571815884</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23263,28 +23435,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08146466048197666</v>
+        <v>0.08563410767767875</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005112791533568029</v>
+        <v>0.005721039001457706</v>
       </c>
       <c r="M5" t="n">
-        <v>6.98229171674887</v>
+        <v>6.960628698633858</v>
       </c>
       <c r="N5" t="n">
-        <v>84.624664522895</v>
+        <v>84.05179952110267</v>
       </c>
       <c r="O5" t="n">
-        <v>9.199166512401817</v>
+        <v>9.167976849943649</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6054753307266</v>
+        <v>366.5637225534213</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23341,28 +23513,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06256558052619172</v>
+        <v>0.06937786178881471</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002824929724881131</v>
+        <v>0.003512213756286409</v>
       </c>
       <c r="M6" t="n">
-        <v>7.870670987949344</v>
+        <v>7.856804401142286</v>
       </c>
       <c r="N6" t="n">
-        <v>90.53913538528164</v>
+        <v>90.05583939730965</v>
       </c>
       <c r="O6" t="n">
-        <v>9.515205483082415</v>
+        <v>9.489775518804944</v>
       </c>
       <c r="P6" t="n">
-        <v>357.3379524863809</v>
+        <v>357.2697245152378</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23419,28 +23591,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01613652328200399</v>
+        <v>0.02428697708034341</v>
       </c>
       <c r="J7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002222958957578403</v>
+        <v>0.0005085229349707232</v>
       </c>
       <c r="M7" t="n">
-        <v>6.91417859108035</v>
+        <v>6.912616437331623</v>
       </c>
       <c r="N7" t="n">
-        <v>76.73501148186028</v>
+        <v>76.45299311951406</v>
       </c>
       <c r="O7" t="n">
-        <v>8.759852252284869</v>
+        <v>8.743740224841659</v>
       </c>
       <c r="P7" t="n">
-        <v>349.1550677243249</v>
+        <v>349.0734344830679</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23497,28 +23669,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04235048530085078</v>
+        <v>-0.03722568193064144</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K8" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002111618812369875</v>
+        <v>0.001651821127606312</v>
       </c>
       <c r="M8" t="n">
-        <v>5.864188311453071</v>
+        <v>5.849470032055283</v>
       </c>
       <c r="N8" t="n">
-        <v>55.48452088201581</v>
+        <v>55.18021208306984</v>
       </c>
       <c r="O8" t="n">
-        <v>7.448793250051703</v>
+        <v>7.428338446992695</v>
       </c>
       <c r="P8" t="n">
-        <v>345.851195057041</v>
+        <v>345.7998620405144</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23556,7 +23728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I516"/>
+  <dimension ref="A1:I520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47799,6 +47971,194 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-41.0774187176086,172.10311514692384</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-41.07675149055176,172.10295103457432</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-41.076077770624025,172.10285938509165</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-41.07540249907586,172.10278499346558</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-41.074722036177526,172.1027685220562</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-41.074040984498744,172.1027585499623</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-41.07336140727696,172.10273202727657</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-41.07741908793732,172.1031110095431</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-41.07675152229387,172.10295067994522</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-41.07607765423676,172.1028606853851</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-41.07540219223749,172.10278842147693</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-41.07472193037088,172.10276970411687</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-41.074040868110984,172.10275985021553</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-41.07336134379261,172.10273273649827</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-41.07741945826588,172.10310687216233</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-41.07675147997106,172.10295115278402</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-41.076078013979135,172.10285666629622</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-41.07540234036637,172.1027867665749</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-41.074722300694106,172.10276556690457</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-41.07404152411449,172.10275252151544</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-41.07336204212035,172.10272493505943</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-41.07741970162457,172.10310415331207</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-41.07675199842537,172.10294536050878</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-41.0760787440441,172.10284850990982</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-41.07540256255965,172.10278428422183</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-41.07472296727557,172.1027581199223</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-41.07404258218369,172.10274070103117</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-41.07336268754399,172.10271772463855</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I520"/>
+  <dimension ref="A1:I521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17596,6 +17596,39 @@
       <c r="I520" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="C521" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="D521" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="E521" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="F521" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="G521" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="H521" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23033,6 +23066,16 @@
       </c>
       <c r="B542" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -23201,28 +23244,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07934661948627919</v>
+        <v>-0.07929024762737702</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005870661014617085</v>
+        <v>0.005883205571049599</v>
       </c>
       <c r="M2" t="n">
-        <v>6.741940356135151</v>
+        <v>6.72936387174646</v>
       </c>
       <c r="N2" t="n">
-        <v>70.24117562476445</v>
+        <v>70.10615508802573</v>
       </c>
       <c r="O2" t="n">
-        <v>8.381000872495148</v>
+        <v>8.372941841911105</v>
       </c>
       <c r="P2" t="n">
-        <v>375.4943188849992</v>
+        <v>375.4937498143514</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23279,28 +23322,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1098740149396563</v>
+        <v>0.1105245345262931</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K3" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008599109083750722</v>
+        <v>0.008730446097628075</v>
       </c>
       <c r="M3" t="n">
-        <v>7.208809990927251</v>
+        <v>7.199464749596548</v>
       </c>
       <c r="N3" t="n">
-        <v>91.69905562041549</v>
+        <v>91.53052113806091</v>
       </c>
       <c r="O3" t="n">
-        <v>9.57596238612159</v>
+        <v>9.567158467280706</v>
       </c>
       <c r="P3" t="n">
-        <v>372.2984249820402</v>
+        <v>372.2918580245221</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23357,28 +23400,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06974309697128321</v>
+        <v>0.0701505665462388</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K4" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004544753503518351</v>
+        <v>0.004613932504888063</v>
       </c>
       <c r="M4" t="n">
-        <v>6.436165600640996</v>
+        <v>6.426732129263876</v>
       </c>
       <c r="N4" t="n">
-        <v>70.19285242181309</v>
+        <v>70.06093033541471</v>
       </c>
       <c r="O4" t="n">
-        <v>8.378117474815753</v>
+        <v>8.370240757314852</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0120571815884</v>
+        <v>373.0079437998492</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23435,28 +23478,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08563410767767875</v>
+        <v>0.08636143974458575</v>
       </c>
       <c r="J5" t="n">
+        <v>520</v>
+      </c>
+      <c r="K5" t="n">
         <v>519</v>
       </c>
-      <c r="K5" t="n">
-        <v>518</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005721039001457706</v>
+        <v>0.00583805137111626</v>
       </c>
       <c r="M5" t="n">
-        <v>6.960628698633858</v>
+        <v>6.952777634753694</v>
       </c>
       <c r="N5" t="n">
-        <v>84.05179952110267</v>
+        <v>83.89963310538299</v>
       </c>
       <c r="O5" t="n">
-        <v>9.167976849943649</v>
+        <v>9.159674290354596</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5637225534213</v>
+        <v>366.5563809645354</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23513,28 +23556,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06937786178881471</v>
+        <v>0.07071332147508975</v>
       </c>
       <c r="J6" t="n">
+        <v>520</v>
+      </c>
+      <c r="K6" t="n">
         <v>519</v>
       </c>
-      <c r="K6" t="n">
-        <v>518</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.003512213756286409</v>
+        <v>0.003659876869695267</v>
       </c>
       <c r="M6" t="n">
-        <v>7.856804401142286</v>
+        <v>7.850746308156005</v>
       </c>
       <c r="N6" t="n">
-        <v>90.05583939730965</v>
+        <v>89.91530007788373</v>
       </c>
       <c r="O6" t="n">
-        <v>9.489775518804944</v>
+        <v>9.4823678518545</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2697245152378</v>
+        <v>357.256243481873</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23591,28 +23634,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02428697708034341</v>
+        <v>0.02597417218087037</v>
       </c>
       <c r="J7" t="n">
+        <v>520</v>
+      </c>
+      <c r="K7" t="n">
         <v>519</v>
       </c>
-      <c r="K7" t="n">
-        <v>518</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0005085229349707232</v>
+        <v>0.0005832619489549717</v>
       </c>
       <c r="M7" t="n">
-        <v>6.912616437331623</v>
+        <v>6.909888426204631</v>
       </c>
       <c r="N7" t="n">
-        <v>76.45299311951406</v>
+        <v>76.35832319627438</v>
       </c>
       <c r="O7" t="n">
-        <v>8.743740224841659</v>
+        <v>8.738324965133442</v>
       </c>
       <c r="P7" t="n">
-        <v>349.0734344830679</v>
+        <v>349.0564027945213</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23669,28 +23712,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03722568193064144</v>
+        <v>-0.03627532806327961</v>
       </c>
       <c r="J8" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K8" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001651821127606312</v>
+        <v>0.00157381280467328</v>
       </c>
       <c r="M8" t="n">
-        <v>5.849470032055283</v>
+        <v>5.84388010840071</v>
       </c>
       <c r="N8" t="n">
-        <v>55.18021208306984</v>
+        <v>55.09076465282848</v>
       </c>
       <c r="O8" t="n">
-        <v>7.428338446992695</v>
+        <v>7.422315316181904</v>
       </c>
       <c r="P8" t="n">
-        <v>345.7998620405144</v>
+        <v>345.7902682733131</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23728,7 +23771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I520"/>
+  <dimension ref="A1:I521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48159,6 +48202,53 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-41.07741970162457,172.10310415331207</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-41.07675178681141,172.10294772470277</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-41.07607866997958,172.10284933736932</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-41.075401430431405,172.10279693240165</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-41.074721189723974,172.1027779785413</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-41.074040434301956,172.10276469661386</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-41.073360835917555,172.10273841027188</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
